--- a/outputs/pipeline_statisticsv3.xlsx
+++ b/outputs/pipeline_statisticsv3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shia\Desktop\Taiwan_Compliance_Agent\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88F3EA5-074F-4F65-A3F8-B1EF38E63C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0753125-A388-4236-A174-D6EEDA2C9321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -41985,7 +41985,7 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
